--- a/ALCORTA 146/Septiembre/Septiembre.xlsx
+++ b/ALCORTA 146/Septiembre/Septiembre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ALCORTA 146\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIOS\Downloads\BRISAS 2025\BASA\ALCORTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2FB7608-3C88-4084-A16E-0720C32B6B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B75AD4-9ED7-474B-A1C9-1D8FBB32B473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,14 +20,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$C$1:$O$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Recibo '!$E$6:$N$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$125</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$124</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="196">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -396,15 +396,6 @@
   </si>
   <si>
     <t>TSG</t>
-  </si>
-  <si>
-    <t>Suterh</t>
-  </si>
-  <si>
-    <t>Seracarh</t>
-  </si>
-  <si>
-    <t>Fatheryh</t>
   </si>
   <si>
     <t>Inquilinos</t>
@@ -465,9 +456,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>Aldo</t>
-  </si>
-  <si>
     <t>Domicilio: Dr. Melo Nº 2958 - 8vo piso (cita previa) Lanus</t>
   </si>
   <si>
@@ -573,27 +561,12 @@
     <t>ES DE CARÁCTER OBLIGATORIO ENVIAR LOS COMPROBANTES DE TRANSFERENCIAS. DE LO CONTRARIO, DEBEN REVISAR EN LA PARTE INFERIOR QUE HAY DEPOSITOS NO IDENTIFICADOS. LA LINEA GRIS CORRESPONDE A UN PLAN DE PAGO EN VIGENCIA.</t>
   </si>
   <si>
-    <t>Reemplazo Sra. Fernanda</t>
-  </si>
-  <si>
     <t>TOTAL REEMPLAZO</t>
   </si>
   <si>
-    <t>Cuota 8</t>
-  </si>
-  <si>
-    <t>ARCA - PENDIENTE PAGO LA DEUDA</t>
-  </si>
-  <si>
     <t>No hay encargado</t>
   </si>
   <si>
-    <t>Recarga anual de matafuegos</t>
-  </si>
-  <si>
-    <t>Pendiente de abono</t>
-  </si>
-  <si>
     <t>E</t>
   </si>
   <si>
@@ -609,25 +582,40 @@
     <t>Mes de SEPTIEMBRE</t>
   </si>
   <si>
-    <t>Sindicatos periodo SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>AYSA  - Mes de SEPTIEMBRE</t>
   </si>
   <si>
-    <t>Fumigacion SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>Metrogas SEPTIEMBRE</t>
   </si>
   <si>
-    <t>Cittadino Cerrajeria - Apertura de porteria y colocacion de cerradura</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Carta documento 4D</t>
+    <t>Cuota 9</t>
+  </si>
+  <si>
+    <t>Cerrajeria Walter - Limpiador de acero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fumigacion </t>
+  </si>
+  <si>
+    <t>ARCA - Parte de deuda</t>
+  </si>
+  <si>
+    <t>Envio carta documento 4D</t>
+  </si>
+  <si>
+    <t>Carta documento 4D - Honorarios</t>
+  </si>
+  <si>
+    <t>Plan de pagos vigente</t>
+  </si>
+  <si>
+    <t>Carta documento 6D- Honorarios</t>
+  </si>
+  <si>
+    <t>Envio carta documento 6D</t>
   </si>
 </sst>
 </file>
@@ -644,7 +632,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -774,6 +762,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1626,6 +1621,10 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1689,6 +1688,9 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1708,9 +1710,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1736,8 +1735,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2103,7 +2100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.44140625" customWidth="1"/>
@@ -2119,7 +2116,7 @@
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="57"/>
       <c r="B1" s="58" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C1" s="57"/>
       <c r="D1" s="57"/>
@@ -2128,7 +2125,7 @@
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="59"/>
       <c r="B2" s="60" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C2" s="61"/>
       <c r="D2" s="61"/>
@@ -2146,10 +2143,10 @@
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="63"/>
       <c r="B4" s="64" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D4" s="64"/>
       <c r="E4" s="65"/>
@@ -2157,7 +2154,7 @@
     <row r="5" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="63"/>
       <c r="B5" s="64" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C5" s="64"/>
       <c r="D5" s="64"/>
@@ -2168,11 +2165,11 @@
         <v>0</v>
       </c>
       <c r="B6" s="67" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C6" s="67"/>
       <c r="D6" s="67" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E6" s="68"/>
     </row>
@@ -2235,34 +2232,34 @@
       <c r="E14" s="69"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="155" t="s">
-        <v>190</v>
-      </c>
-      <c r="B15" s="155"/>
-      <c r="C15" s="155"/>
-      <c r="D15" s="155"/>
-      <c r="E15" s="155"/>
+      <c r="A15" s="157" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" s="157"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="157"/>
+      <c r="E15" s="157"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="155"/>
-      <c r="B16" s="155"/>
-      <c r="C16" s="155"/>
-      <c r="D16" s="155"/>
-      <c r="E16" s="155"/>
+      <c r="A16" s="157"/>
+      <c r="B16" s="157"/>
+      <c r="C16" s="157"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="157"/>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="155"/>
-      <c r="B17" s="155"/>
-      <c r="C17" s="155"/>
-      <c r="D17" s="155"/>
-      <c r="E17" s="155"/>
+      <c r="A17" s="157"/>
+      <c r="B17" s="157"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="157"/>
+      <c r="E17" s="157"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="155"/>
-      <c r="B18" s="155"/>
-      <c r="C18" s="155"/>
-      <c r="D18" s="155"/>
-      <c r="E18" s="155"/>
+      <c r="A18" s="157"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="157"/>
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="69"/>
@@ -2286,39 +2283,39 @@
       <c r="E21" s="69"/>
     </row>
     <row r="22" spans="1:5" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="156"/>
-      <c r="B22" s="157"/>
-      <c r="C22" s="157"/>
-      <c r="D22" s="157"/>
-      <c r="E22" s="157"/>
+      <c r="A22" s="158"/>
+      <c r="B22" s="159"/>
+      <c r="C22" s="159"/>
+      <c r="D22" s="159"/>
+      <c r="E22" s="159"/>
     </row>
     <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="157"/>
-      <c r="B23" s="157"/>
-      <c r="C23" s="157"/>
-      <c r="D23" s="157"/>
-      <c r="E23" s="157"/>
+      <c r="A23" s="159"/>
+      <c r="B23" s="159"/>
+      <c r="C23" s="159"/>
+      <c r="D23" s="159"/>
+      <c r="E23" s="159"/>
     </row>
     <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="157"/>
-      <c r="B24" s="157"/>
-      <c r="C24" s="157"/>
-      <c r="D24" s="157"/>
-      <c r="E24" s="157"/>
+      <c r="A24" s="159"/>
+      <c r="B24" s="159"/>
+      <c r="C24" s="159"/>
+      <c r="D24" s="159"/>
+      <c r="E24" s="159"/>
     </row>
     <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="157"/>
-      <c r="B25" s="157"/>
-      <c r="C25" s="157"/>
-      <c r="D25" s="157"/>
-      <c r="E25" s="157"/>
+      <c r="A25" s="159"/>
+      <c r="B25" s="159"/>
+      <c r="C25" s="159"/>
+      <c r="D25" s="159"/>
+      <c r="E25" s="159"/>
     </row>
     <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="157"/>
-      <c r="B26" s="157"/>
-      <c r="C26" s="157"/>
-      <c r="D26" s="157"/>
-      <c r="E26" s="157"/>
+      <c r="A26" s="159"/>
+      <c r="B26" s="159"/>
+      <c r="C26" s="159"/>
+      <c r="D26" s="159"/>
+      <c r="E26" s="159"/>
     </row>
     <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="69"/>
@@ -2347,7 +2344,7 @@
     </row>
     <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="75" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B30" s="76"/>
       <c r="C30" s="76"/>
@@ -2380,54 +2377,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="76" t="s">
-        <v>181</v>
-      </c>
+    <row r="34" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="76"/>
       <c r="B34" s="76"/>
       <c r="C34" s="76"/>
-      <c r="D34" s="77">
-        <v>174000</v>
-      </c>
+      <c r="D34" s="77"/>
       <c r="E34" s="76"/>
-      <c r="G34">
-        <v>235611</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="76"/>
       <c r="B35" s="76"/>
       <c r="C35" s="76"/>
       <c r="D35" s="77"/>
       <c r="E35" s="76"/>
-      <c r="G35" s="5">
-        <f>E33+E37-G34</f>
-        <v>-61611</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G35" s="5"/>
+    </row>
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="76"/>
       <c r="B36" s="76"/>
       <c r="C36" s="76"/>
       <c r="D36" s="80"/>
       <c r="E36" s="76"/>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="20" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
       <c r="D37" s="36"/>
       <c r="E37" s="79">
         <f>SUM(D34:D36)</f>
-        <v>174000</v>
+        <v>0</v>
       </c>
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
@@ -2436,42 +2423,40 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="76" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B39" s="76" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C39" s="76"/>
-      <c r="D39" s="196">
+      <c r="D39" s="77">
         <v>30000</v>
       </c>
       <c r="E39" s="82"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="76" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B40" s="76" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C40" s="76"/>
-      <c r="D40" s="196">
+      <c r="D40" s="77">
         <v>123100</v>
       </c>
       <c r="E40" s="82" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G40" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="76"/>
       <c r="B41" s="76"/>
       <c r="C41" s="76"/>
-      <c r="D41" s="197">
-        <v>122000</v>
-      </c>
+      <c r="D41" s="17"/>
       <c r="E41" s="82"/>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2501,7 +2486,7 @@
       </c>
       <c r="B44" s="76"/>
       <c r="C44" s="76" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D44" s="17">
         <v>28208</v>
@@ -2538,682 +2523,675 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="76" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B48" s="76"/>
       <c r="C48" s="76"/>
       <c r="D48" s="17">
-        <v>0</v>
+        <v>1124286.96</v>
       </c>
       <c r="E48" s="24"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="76" t="s">
-        <v>193</v>
-      </c>
-      <c r="B49" s="76" t="s">
-        <v>125</v>
-      </c>
+      <c r="A49" s="76"/>
+      <c r="B49" s="76"/>
       <c r="C49" s="76"/>
-      <c r="D49" s="17">
-        <v>0</v>
-      </c>
+      <c r="D49" s="17"/>
       <c r="E49" s="24"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="76" t="str">
-        <f>A49</f>
-        <v>Sindicatos periodo SEPTIEMBRE</v>
-      </c>
-      <c r="B50" s="76" t="s">
-        <v>123</v>
-      </c>
-      <c r="C50" s="76"/>
-      <c r="D50" s="17">
-        <v>0</v>
-      </c>
-      <c r="E50" s="24"/>
+    <row r="50" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="87">
+        <f>SUM(D48:D49)</f>
+        <v>1124286.96</v>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="76" t="str">
-        <f>A50</f>
-        <v>Sindicatos periodo SEPTIEMBRE</v>
-      </c>
-      <c r="B51" s="76" t="s">
-        <v>124</v>
-      </c>
-      <c r="C51" s="76"/>
-      <c r="D51" s="17">
-        <v>0</v>
-      </c>
-      <c r="E51" s="84"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="76"/>
-      <c r="B52" s="76"/>
+      <c r="A51" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B51" s="37"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="86"/>
+    </row>
+    <row r="52" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="76" t="s">
+        <v>184</v>
+      </c>
+      <c r="B52" s="88"/>
       <c r="C52" s="76"/>
-      <c r="D52" s="17"/>
+      <c r="D52" s="17">
+        <v>488319.13</v>
+      </c>
       <c r="E52" s="24"/>
     </row>
-    <row r="53" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="37"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="27"/>
-      <c r="E53" s="87">
-        <f>SUM(D48:D52)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B54" s="37"/>
-      <c r="C54" s="37"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="86"/>
-    </row>
-    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="88" t="s">
+        <v>165</v>
+      </c>
+      <c r="B53" s="88"/>
+      <c r="C53" s="76"/>
+      <c r="D53" s="17">
+        <v>71200</v>
+      </c>
+      <c r="E53" s="17"/>
+    </row>
+    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="76" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="89"/>
+      <c r="C54" s="90"/>
+      <c r="D54" s="17">
+        <v>0</v>
+      </c>
+      <c r="E54" s="24"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="76" t="s">
-        <v>194</v>
-      </c>
-      <c r="B55" s="88"/>
-      <c r="C55" s="76"/>
-      <c r="D55" s="141">
-        <v>488319.13</v>
+        <v>189</v>
+      </c>
+      <c r="B55" s="76"/>
+      <c r="C55" s="90"/>
+      <c r="D55" s="17">
+        <v>95000</v>
       </c>
       <c r="E55" s="24"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="88" t="s">
-        <v>169</v>
-      </c>
-      <c r="B56" s="88"/>
-      <c r="C56" s="76"/>
-      <c r="D56" s="141">
-        <v>71200</v>
-      </c>
-      <c r="E56" s="17"/>
-    </row>
-    <row r="57" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="76" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="76"/>
+      <c r="C56" s="139"/>
+      <c r="D56" s="155">
+        <v>111255.93</v>
+      </c>
+      <c r="E56" s="24"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="76" t="s">
-        <v>120</v>
-      </c>
-      <c r="B57" s="89"/>
-      <c r="C57" s="90"/>
+        <v>140</v>
+      </c>
+      <c r="B57" s="76"/>
+      <c r="C57" s="141"/>
       <c r="D57" s="17">
-        <v>0</v>
-      </c>
-      <c r="E57" s="24"/>
-    </row>
-    <row r="58" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>110899</v>
+      </c>
+      <c r="E57" s="82"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="76" t="s">
-        <v>197</v>
-      </c>
-      <c r="B58" s="89"/>
-      <c r="C58" s="90"/>
-      <c r="D58" s="141">
-        <v>108000</v>
-      </c>
-      <c r="E58" s="24"/>
-    </row>
-    <row r="59" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+      <c r="B58" s="76"/>
+      <c r="C58" s="141"/>
+      <c r="D58" s="17">
+        <v>15455.5</v>
+      </c>
+      <c r="E58" s="82" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="76" t="s">
-        <v>186</v>
-      </c>
-      <c r="B59" s="89"/>
-      <c r="C59" s="90"/>
+        <v>121</v>
+      </c>
+      <c r="B59" s="76"/>
+      <c r="C59" s="141"/>
       <c r="D59" s="17">
-        <v>217299.9</v>
-      </c>
-      <c r="E59" s="24"/>
+        <v>3535.19</v>
+      </c>
+      <c r="E59" s="82"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="76" t="s">
-        <v>195</v>
-      </c>
-      <c r="B60" s="76" t="s">
-        <v>187</v>
-      </c>
-      <c r="C60" s="90"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="24"/>
+        <v>121</v>
+      </c>
+      <c r="B60" s="76"/>
+      <c r="C60" s="141"/>
+      <c r="D60" s="17">
+        <v>7462.34</v>
+      </c>
+      <c r="E60" s="139"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="76" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="B61" s="76"/>
-      <c r="C61" s="139"/>
-      <c r="D61" s="139">
-        <v>110899</v>
+      <c r="C61" s="76"/>
+      <c r="D61" s="17">
+        <v>14863.04</v>
       </c>
       <c r="E61" s="24"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="76" t="s">
-        <v>115</v>
-      </c>
-      <c r="B62" s="76"/>
-      <c r="C62" s="141"/>
-      <c r="D62" s="141">
-        <v>15455.5</v>
-      </c>
-      <c r="E62" s="82" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="76" t="s">
-        <v>121</v>
-      </c>
-      <c r="B63" s="76"/>
-      <c r="C63" s="141"/>
-      <c r="D63" s="141">
-        <v>3535.19</v>
-      </c>
-      <c r="E63" s="82"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="76" t="s">
-        <v>121</v>
-      </c>
-      <c r="B64" s="76"/>
-      <c r="C64" s="141"/>
-      <c r="D64" s="141">
-        <v>7444.09</v>
-      </c>
-      <c r="E64" s="139"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="76"/>
+      <c r="B62" s="91"/>
+      <c r="C62" s="92"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="84"/>
+    </row>
+    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="85">
+        <f>SUM(D52:D62)</f>
+        <v>917990.13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B64" s="20"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="85"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="76" t="s">
-        <v>196</v>
+        <v>147</v>
       </c>
       <c r="B65" s="76"/>
       <c r="C65" s="76"/>
-      <c r="D65" s="141">
-        <v>14863.04</v>
-      </c>
-      <c r="E65" s="24"/>
-    </row>
-    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="76"/>
-      <c r="B66" s="91"/>
-      <c r="C66" s="92"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="84"/>
-    </row>
-    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B67" s="20"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="85">
-        <f>SUM(D55:D66)</f>
-        <v>1037015.85</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="85"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="76" t="s">
-        <v>151</v>
-      </c>
-      <c r="B69" s="76"/>
-      <c r="C69" s="76"/>
-      <c r="D69" s="17">
+      <c r="D65" s="17">
         <v>49294.58</v>
       </c>
-      <c r="E69" s="82"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="76"/>
-      <c r="B70" s="76"/>
-      <c r="C70" s="76"/>
-      <c r="D70" s="197">
-        <v>19000</v>
-      </c>
-      <c r="E70" s="82"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E65" s="82"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66" s="76"/>
+      <c r="C66" s="76"/>
+      <c r="D66" s="17">
+        <v>22000</v>
+      </c>
+      <c r="E66" s="82"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="76" t="s">
+        <v>186</v>
+      </c>
+      <c r="B67" s="76"/>
+      <c r="C67" s="76"/>
+      <c r="D67" s="17">
+        <f>135700</f>
+        <v>135700</v>
+      </c>
+      <c r="E67" s="82"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="76" t="s">
+        <v>139</v>
+      </c>
+      <c r="B68" s="76"/>
+      <c r="C68" s="76"/>
+      <c r="D68" s="24">
+        <v>2400</v>
+      </c>
+      <c r="E68" s="24"/>
+    </row>
+    <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="93">
+        <f>SUM(D65:D68)</f>
+        <v>209394.58000000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B70" s="20"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="85"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="76" t="s">
-        <v>198</v>
+        <v>36</v>
       </c>
       <c r="B71" s="76"/>
       <c r="C71" s="76"/>
-      <c r="D71" s="141">
-        <f>22000+135700</f>
-        <v>157700</v>
-      </c>
-      <c r="E71" s="82"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="76" t="s">
-        <v>142</v>
-      </c>
+      <c r="D71" s="17">
+        <v>67395.62</v>
+      </c>
+      <c r="E71" s="94"/>
+    </row>
+    <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="75"/>
       <c r="B72" s="76"/>
       <c r="C72" s="76"/>
-      <c r="D72" s="136">
-        <v>2400</v>
-      </c>
-      <c r="E72" s="24"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="76"/>
-      <c r="B73" s="76"/>
-      <c r="C73" s="76"/>
-      <c r="D73" s="24"/>
-      <c r="E73" s="17"/>
-    </row>
-    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="20" t="s">
+      <c r="D72" s="17"/>
+      <c r="E72" s="95"/>
+    </row>
+    <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B73" s="20"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="85">
+        <f>SUM(D71:D72)</f>
+        <v>67395.62</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="76"/>
+      <c r="B74" s="76"/>
+      <c r="C74" s="76"/>
+      <c r="D74" s="76"/>
+      <c r="E74" s="96"/>
+    </row>
+    <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="97" t="s">
+        <v>169</v>
+      </c>
+      <c r="B75" s="97"/>
+      <c r="C75" s="97"/>
+      <c r="D75" s="98"/>
+      <c r="E75" s="99">
+        <f>5100000-2500375.29</f>
+        <v>2599624.71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="100"/>
+      <c r="B76" s="69"/>
+      <c r="C76" s="69"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="101"/>
+      <c r="F76" s="31"/>
+    </row>
+    <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="102" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" s="103"/>
+      <c r="C77" s="104"/>
+      <c r="D77" s="104"/>
+      <c r="E77" s="105">
+        <f>(SUM(E30:E75))</f>
+        <v>5100000</v>
+      </c>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="69"/>
+      <c r="B78" s="69"/>
+      <c r="C78" s="69"/>
+      <c r="D78" s="69"/>
+      <c r="E78" s="69"/>
+    </row>
+    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="69"/>
+      <c r="B79" s="69"/>
+      <c r="C79" s="69"/>
+      <c r="D79" s="69"/>
+      <c r="E79" s="69"/>
+      <c r="F79" s="31"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="168" t="s">
+        <v>143</v>
+      </c>
+      <c r="B80" s="169"/>
+      <c r="C80" s="106"/>
+      <c r="D80" s="69"/>
+      <c r="E80" s="69"/>
+    </row>
+    <row r="81" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="160"/>
+      <c r="B81" s="161"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="69"/>
+      <c r="E81" s="69"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="162"/>
+      <c r="B82" s="163"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="69"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="164"/>
+      <c r="B83" s="165"/>
+      <c r="C83" s="107"/>
+      <c r="D83" s="69"/>
+      <c r="E83" s="108"/>
+    </row>
+    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="93">
-        <f>SUM(D69:D73)</f>
-        <v>228394.58000000002</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="12"/>
-      <c r="E75" s="85"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="76" t="s">
-        <v>36</v>
-      </c>
-      <c r="B76" s="76"/>
-      <c r="C76" s="76"/>
-      <c r="D76" s="17">
-        <f>15700+69662.2</f>
-        <v>85362.2</v>
-      </c>
-      <c r="E76" s="94"/>
-    </row>
-    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="75"/>
-      <c r="B77" s="76"/>
-      <c r="C77" s="76"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="95"/>
-    </row>
-    <row r="78" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B78" s="20"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="85">
-        <f>SUM(D76:D77)</f>
-        <v>85362.2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="76"/>
-      <c r="B79" s="76"/>
-      <c r="C79" s="76"/>
-      <c r="D79" s="76"/>
-      <c r="E79" s="96"/>
-    </row>
-    <row r="80" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="97" t="s">
-        <v>173</v>
-      </c>
-      <c r="B80" s="97"/>
-      <c r="C80" s="97"/>
-      <c r="D80" s="98"/>
-      <c r="E80" s="99">
-        <f>5100000-1499021.75</f>
-        <v>3600978.25</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="100"/>
-      <c r="B81" s="69"/>
-      <c r="C81" s="69"/>
-      <c r="D81" s="69"/>
-      <c r="E81" s="101"/>
-      <c r="F81" s="31"/>
-    </row>
-    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="102" t="s">
-        <v>37</v>
-      </c>
-      <c r="B82" s="103"/>
-      <c r="C82" s="104"/>
-      <c r="D82" s="104"/>
-      <c r="E82" s="105">
-        <f>(SUM(E30:E80))</f>
-        <v>5307058.88</v>
-      </c>
-      <c r="F82" s="31"/>
-      <c r="G82" s="31"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="69"/>
-      <c r="B83" s="69"/>
-      <c r="C83" s="69"/>
-      <c r="D83" s="69"/>
-      <c r="E83" s="69"/>
-    </row>
-    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="69"/>
-      <c r="B84" s="69"/>
-      <c r="C84" s="69"/>
+      <c r="B84" s="167"/>
+      <c r="C84" s="109">
+        <f>SUM(C81:C83)</f>
+        <v>0</v>
+      </c>
       <c r="D84" s="69"/>
       <c r="E84" s="69"/>
-      <c r="F84" s="31"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="166" t="s">
-        <v>147</v>
-      </c>
-      <c r="B85" s="167"/>
-      <c r="C85" s="106"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="69"/>
+      <c r="B85" s="69"/>
+      <c r="C85" s="69"/>
       <c r="D85" s="69"/>
       <c r="E85" s="69"/>
     </row>
-    <row r="86" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="158"/>
-      <c r="B86" s="159"/>
-      <c r="C86" s="17"/>
-      <c r="D86" s="69"/>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="110" t="s">
+        <v>148</v>
+      </c>
+      <c r="B86" s="110"/>
+      <c r="C86" s="111"/>
+      <c r="D86" s="112"/>
       <c r="E86" s="69"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="160"/>
-      <c r="B87" s="161"/>
-      <c r="C87" s="17"/>
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="69"/>
+      <c r="B87" s="69"/>
+      <c r="C87" s="69"/>
       <c r="D87" s="69"/>
       <c r="E87" s="69"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="162"/>
-      <c r="B88" s="163"/>
-      <c r="C88" s="107"/>
+    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="113" t="s">
+        <v>38</v>
+      </c>
+      <c r="B88" s="114">
+        <f>E77</f>
+        <v>5100000</v>
+      </c>
+      <c r="C88" s="69"/>
       <c r="D88" s="69"/>
       <c r="E88" s="108"/>
     </row>
-    <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="164" t="s">
-        <v>14</v>
-      </c>
-      <c r="B89" s="165"/>
-      <c r="C89" s="109">
-        <f>SUM(C86:C88)</f>
-        <v>0</v>
-      </c>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="115" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" s="116">
+        <f>E77-E75</f>
+        <v>2500375.29</v>
+      </c>
+      <c r="C89" s="69"/>
       <c r="D89" s="69"/>
       <c r="E89" s="69"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="69"/>
-      <c r="B90" s="69"/>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="117" t="s">
+        <v>145</v>
+      </c>
+      <c r="B90" s="118">
+        <f>C84+C86</f>
+        <v>0</v>
+      </c>
       <c r="C90" s="69"/>
       <c r="D90" s="69"/>
       <c r="E90" s="69"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="110" t="s">
-        <v>152</v>
-      </c>
-      <c r="B91" s="110"/>
-      <c r="C91" s="111"/>
-      <c r="D91" s="112"/>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="B91" s="118">
+        <f>C84</f>
+        <v>0</v>
+      </c>
+      <c r="C91" s="69"/>
+      <c r="D91" s="69"/>
       <c r="E91" s="69"/>
     </row>
-    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="69"/>
-      <c r="B92" s="69"/>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="117" t="s">
+        <v>146</v>
+      </c>
+      <c r="B92" s="118">
+        <f>B89+B91</f>
+        <v>2500375.29</v>
+      </c>
       <c r="C92" s="69"/>
       <c r="D92" s="69"/>
       <c r="E92" s="69"/>
     </row>
-    <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="113" t="s">
-        <v>38</v>
-      </c>
-      <c r="B93" s="114">
-        <f>E82</f>
-        <v>5307058.88</v>
-      </c>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="69"/>
+      <c r="B93" s="69"/>
       <c r="C93" s="69"/>
       <c r="D93" s="69"/>
-      <c r="E93" s="108"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" s="115" t="s">
-        <v>39</v>
-      </c>
-      <c r="B94" s="116">
-        <f>E82-E80</f>
-        <v>1706080.63</v>
-      </c>
-      <c r="C94" s="69"/>
+      <c r="E93" s="69"/>
+    </row>
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="159"/>
+      <c r="B94" s="159"/>
+      <c r="C94" s="159"/>
       <c r="D94" s="69"/>
       <c r="E94" s="69"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="117" t="s">
-        <v>149</v>
-      </c>
-      <c r="B95" s="118">
-        <f>C89+C91</f>
-        <v>0</v>
-      </c>
-      <c r="C95" s="69"/>
+    <row r="95" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="159"/>
+      <c r="B95" s="159"/>
+      <c r="C95" s="159"/>
       <c r="D95" s="69"/>
       <c r="E95" s="69"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="117" t="s">
-        <v>148</v>
-      </c>
-      <c r="B96" s="118">
-        <f>C89</f>
-        <v>0</v>
-      </c>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="69"/>
+      <c r="B96" s="69"/>
       <c r="C96" s="69"/>
       <c r="D96" s="69"/>
       <c r="E96" s="69"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="117" t="s">
-        <v>150</v>
-      </c>
-      <c r="B97" s="118">
-        <f>B94+B96</f>
-        <v>1706080.63</v>
-      </c>
-      <c r="C97" s="69"/>
+      <c r="A97" s="119" t="s">
+        <v>161</v>
+      </c>
+      <c r="B97" s="120"/>
+      <c r="C97" s="121"/>
       <c r="D97" s="69"/>
       <c r="E97" s="69"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="69"/>
-      <c r="B98" s="69"/>
-      <c r="C98" s="69"/>
+      <c r="A98" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B98" s="120">
+        <v>-560589.97402956639</v>
+      </c>
+      <c r="C98" s="122"/>
       <c r="D98" s="69"/>
       <c r="E98" s="69"/>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="157"/>
-      <c r="B99" s="157"/>
-      <c r="C99" s="157"/>
-      <c r="D99" s="69"/>
+    <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="123" t="s">
+        <v>42</v>
+      </c>
+      <c r="B99" s="124">
+        <f>PRORRATEO!I42</f>
+        <v>4055849.1224055998</v>
+      </c>
+      <c r="C99" s="121"/>
+      <c r="D99" s="108"/>
       <c r="E99" s="69"/>
     </row>
-    <row r="100" spans="1:5" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="157"/>
-      <c r="B100" s="157"/>
-      <c r="C100" s="157"/>
-      <c r="D100" s="69"/>
+    <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="123" t="s">
+        <v>192</v>
+      </c>
+      <c r="B100" s="138">
+        <v>-74376</v>
+      </c>
+      <c r="C100" s="121"/>
+      <c r="D100" s="108"/>
       <c r="E100" s="69"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="69"/>
-      <c r="B101" s="69"/>
-      <c r="C101" s="69"/>
-      <c r="D101" s="69"/>
+    <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="123" t="s">
+        <v>191</v>
+      </c>
+      <c r="B101" s="138">
+        <v>-19000</v>
+      </c>
+      <c r="C101" s="121"/>
+      <c r="D101" s="108"/>
       <c r="E101" s="69"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="119" t="s">
-        <v>165</v>
-      </c>
-      <c r="B102" s="120"/>
+    <row r="102" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="123" t="s">
+        <v>194</v>
+      </c>
+      <c r="B102" s="138">
+        <v>-74376</v>
+      </c>
       <c r="C102" s="121"/>
-      <c r="D102" s="69"/>
+      <c r="D102" s="108"/>
       <c r="E102" s="69"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B103" s="120">
-        <v>-5554956.6072822874</v>
-      </c>
-      <c r="C103" s="122"/>
-      <c r="D103" s="69"/>
+    <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="123" t="s">
+        <v>195</v>
+      </c>
+      <c r="B103" s="138">
+        <v>-19000</v>
+      </c>
+      <c r="C103" s="121"/>
+      <c r="D103" s="108"/>
       <c r="E103" s="69"/>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="123" t="s">
-        <v>42</v>
-      </c>
-      <c r="B104" s="124">
-        <f>PRORRATEO!I42</f>
-        <v>6362289.1432527211</v>
+        <v>193</v>
+      </c>
+      <c r="B104" s="138">
+        <v>61700</v>
       </c>
       <c r="C104" s="121"/>
       <c r="D104" s="108"/>
       <c r="E104" s="69"/>
     </row>
-    <row r="105" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="123" t="s">
-        <v>199</v>
+    <row r="105" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="125" t="s">
+        <v>41</v>
       </c>
       <c r="B105" s="138">
-        <v>-74376</v>
+        <f>-(B92+B113)</f>
+        <v>-2266376.29</v>
       </c>
       <c r="C105" s="121"/>
-      <c r="D105" s="108"/>
+      <c r="D105" s="69"/>
       <c r="E105" s="69"/>
     </row>
-    <row r="106" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="125" t="s">
-        <v>41</v>
-      </c>
-      <c r="B106" s="138">
-        <f>-(B97+B114)</f>
-        <v>-1567525.13</v>
-      </c>
-      <c r="C106" s="121"/>
-      <c r="D106" s="69"/>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="126" t="s">
+        <v>14</v>
+      </c>
+      <c r="B106" s="40">
+        <f>SUM(B98:B105)</f>
+        <v>1103830.8583760336</v>
+      </c>
+      <c r="C106" s="127"/>
+      <c r="D106" s="108"/>
       <c r="E106" s="69"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="126" t="s">
-        <v>14</v>
-      </c>
-      <c r="B107" s="40">
-        <f>SUM(B103:B106)</f>
-        <v>-834568.59402956627</v>
-      </c>
+      <c r="A107" s="69"/>
+      <c r="B107" s="128"/>
       <c r="C107" s="127"/>
-      <c r="D107" s="108"/>
+      <c r="D107" s="69"/>
       <c r="E107" s="69"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="69"/>
-      <c r="B108" s="128"/>
+      <c r="B108" s="129"/>
       <c r="C108" s="127"/>
       <c r="D108" s="69"/>
       <c r="E108" s="69"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="69"/>
-      <c r="B109" s="129"/>
-      <c r="C109" s="127"/>
-      <c r="D109" s="69"/>
-      <c r="E109" s="69"/>
+      <c r="B109" s="128"/>
+      <c r="C109" s="130"/>
+      <c r="D109" s="131"/>
+      <c r="E109" s="131"/>
     </row>
     <row r="110" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="69"/>
-      <c r="B110" s="128"/>
+      <c r="A110" s="132" t="s">
+        <v>43</v>
+      </c>
+      <c r="B110" s="24"/>
       <c r="C110" s="130"/>
       <c r="D110" s="131"/>
-      <c r="E110" s="131"/>
-    </row>
-    <row r="111" spans="1:5" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="132" t="s">
-        <v>43</v>
-      </c>
-      <c r="B111" s="24"/>
+      <c r="E110" s="133"/>
+    </row>
+    <row r="111" spans="1:5" s="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="B111" s="24">
+        <v>117641.86240000001</v>
+      </c>
       <c r="C111" s="130"/>
-      <c r="D111" s="131"/>
+      <c r="D111" s="133"/>
       <c r="E111" s="133"/>
     </row>
-    <row r="112" spans="1:5" s="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="76" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B112" s="24">
-        <v>0</v>
-      </c>
-      <c r="C112" s="130"/>
-      <c r="D112" s="133"/>
-      <c r="E112" s="133"/>
-    </row>
-    <row r="113" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <f>PRORRATEO!I43</f>
+        <v>169830.44620100007</v>
+      </c>
+      <c r="C112" s="127"/>
+      <c r="D112" s="108"/>
+      <c r="E112" s="69"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="76" t="s">
-        <v>33</v>
-      </c>
-      <c r="B113" s="24">
-        <f>PRORRATEO!I43</f>
-        <v>248741.1024</v>
+        <v>41</v>
+      </c>
+      <c r="B113" s="39">
+        <f>-(D40+D57)</f>
+        <v>-233999</v>
       </c>
       <c r="C113" s="127"/>
-      <c r="D113" s="108"/>
+      <c r="D113" s="69"/>
       <c r="E113" s="69"/>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="76" t="s">
-        <v>41</v>
-      </c>
-      <c r="B114" s="39">
-        <f>-(D40+D62)</f>
-        <v>-138555.5</v>
-      </c>
+      <c r="A114" s="76"/>
+      <c r="B114" s="39"/>
       <c r="C114" s="127"/>
       <c r="D114" s="69"/>
       <c r="E114" s="69"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="76"/>
-      <c r="B115" s="39"/>
-      <c r="C115" s="127"/>
+    <row r="115" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="137"/>
+      <c r="B115" s="136"/>
+      <c r="C115" s="134"/>
       <c r="D115" s="69"/>
       <c r="E115" s="69"/>
     </row>
@@ -3224,73 +3202,66 @@
       <c r="D116" s="69"/>
       <c r="E116" s="69"/>
     </row>
-    <row r="117" spans="1:13" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="137"/>
-      <c r="B117" s="136"/>
-      <c r="C117" s="134"/>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="132" t="s">
+        <v>44</v>
+      </c>
+      <c r="B117" s="40">
+        <f>SUM(B111:B116)</f>
+        <v>53473.308601000113</v>
+      </c>
+      <c r="C117" s="121"/>
       <c r="D117" s="69"/>
       <c r="E117" s="69"/>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="132" t="s">
-        <v>44</v>
-      </c>
-      <c r="B118" s="40">
-        <f>SUM(B112:B117)</f>
-        <v>110185.6024</v>
-      </c>
-      <c r="C118" s="121"/>
+      <c r="A118" s="69"/>
+      <c r="B118" s="69"/>
+      <c r="C118" s="69"/>
       <c r="D118" s="69"/>
       <c r="E118" s="69"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="69"/>
-      <c r="B119" s="69"/>
-      <c r="C119" s="69"/>
-      <c r="D119" s="69"/>
-      <c r="E119" s="69"/>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A120" s="156" t="s">
+        <v>149</v>
+      </c>
+      <c r="B120" s="156"/>
+      <c r="C120" s="156"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="154" t="s">
-        <v>153</v>
-      </c>
-      <c r="B121" s="154"/>
-      <c r="C121" s="154"/>
+      <c r="A121" s="156"/>
+      <c r="B121" s="156"/>
+      <c r="C121" s="156"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="154"/>
-      <c r="B122" s="154"/>
-      <c r="C122" s="154"/>
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="23"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
-      <c r="C123" s="23"/>
+      <c r="A123" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B123" s="32"/>
+      <c r="C123" s="33">
+        <f>SUM(C122:C122)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B124" s="32"/>
-      <c r="C124" s="33">
-        <f>SUM(C123:C123)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M125" s="4"/>
+      <c r="M124" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A121:C122"/>
+    <mergeCell ref="A120:C121"/>
     <mergeCell ref="A15:E18"/>
     <mergeCell ref="A22:E26"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A99:C100"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A94:C95"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3337,10 +3308,10 @@
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="176">
+      <c r="N1" s="179">
         <v>5100000</v>
       </c>
-      <c r="O1" s="176"/>
+      <c r="O1" s="179"/>
       <c r="P1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3359,70 +3330,70 @@
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="175"/>
-      <c r="O2" s="175"/>
+      <c r="N2" s="178"/>
+      <c r="O2" s="178"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="168" t="s">
+      <c r="A3" s="170" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="172" t="s">
+      <c r="C3" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="172" t="s">
+      <c r="D3" s="174" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="172" t="s">
-        <v>126</v>
-      </c>
-      <c r="F3" s="168" t="s">
+      <c r="E3" s="174" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="170" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="168" t="s">
+      <c r="H3" s="170" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="14"/>
-      <c r="J3" s="179" t="s">
-        <v>139</v>
-      </c>
-      <c r="K3" s="177" t="s">
+      <c r="J3" s="182" t="s">
+        <v>136</v>
+      </c>
+      <c r="K3" s="180" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="177" t="s">
+      <c r="L3" s="180" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="177" t="s">
-        <v>179</v>
-      </c>
-      <c r="N3" s="177" t="s">
+      <c r="M3" s="180" t="s">
+        <v>175</v>
+      </c>
+      <c r="N3" s="180" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="177" t="s">
+      <c r="O3" s="180" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="169"/>
-      <c r="B4" s="171"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="174"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="169"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="173"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="176"/>
+      <c r="F4" s="171"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="171"/>
       <c r="I4" s="15"/>
-      <c r="J4" s="180"/>
-      <c r="K4" s="178"/>
-      <c r="L4" s="181"/>
-      <c r="M4" s="181"/>
-      <c r="N4" s="181"/>
-      <c r="O4" s="178"/>
+      <c r="J4" s="183"/>
+      <c r="K4" s="181"/>
+      <c r="L4" s="184"/>
+      <c r="M4" s="184"/>
+      <c r="N4" s="184"/>
+      <c r="O4" s="181"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -3440,11 +3411,11 @@
         <v>2.63</v>
       </c>
       <c r="G5" s="24">
-        <v>196453.12315792553</v>
+        <v>134130.07195792551</v>
       </c>
       <c r="H5" s="29">
-        <f>318956-G37</f>
-        <v>196453.05120000002</v>
+        <f>217770-G37</f>
+        <v>134130</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>119</v>
@@ -3483,16 +3454,16 @@
         <v>83</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F6" s="1">
         <v>3.33</v>
       </c>
       <c r="G6" s="24">
-        <v>466820.38216694933</v>
+        <v>387909.38216694933</v>
       </c>
       <c r="H6" s="29">
-        <v>248741</v>
+        <v>169830</v>
       </c>
       <c r="I6" s="13" t="s">
         <v>119</v>
@@ -3536,17 +3507,17 @@
         <v>3.32</v>
       </c>
       <c r="G7" s="24">
-        <v>247987.54879999999</v>
+        <v>169307.54879999999</v>
       </c>
       <c r="H7" s="29">
-        <v>248000</v>
+        <v>169300</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>119</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" si="0"/>
-        <v>12.451200000010431</v>
+        <v>-7.5487999999895692</v>
       </c>
       <c r="K7" s="38">
         <f t="shared" si="1"/>
@@ -3559,11 +3530,11 @@
       <c r="M7" s="23"/>
       <c r="N7" s="23">
         <f t="shared" ref="N7:N40" si="4">L7+K7-J7+M7</f>
-        <v>169307.54879999999</v>
+        <v>169327.54879999999</v>
       </c>
       <c r="O7" s="23">
         <f t="shared" si="3"/>
-        <v>179466.001728</v>
+        <v>179487.20172799999</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -3582,18 +3553,18 @@
         <v>3.42</v>
       </c>
       <c r="G8" s="24">
-        <v>610089.1281354035</v>
+        <v>529509.1281354035</v>
       </c>
       <c r="H8" s="29">
-        <f>255000</f>
-        <v>255000</v>
+        <f>90000+60000</f>
+        <v>150000</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>119</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" si="0"/>
-        <v>-355089.1281354035</v>
+        <v>-379509.1281354035</v>
       </c>
       <c r="K8" s="38">
         <f t="shared" si="1"/>
@@ -3606,11 +3577,11 @@
       <c r="M8" s="23"/>
       <c r="N8" s="23">
         <f t="shared" si="4"/>
-        <v>529509.1281354035</v>
+        <v>553929.1281354035</v>
       </c>
       <c r="O8" s="23">
         <f t="shared" si="3"/>
-        <v>561279.67582352774</v>
+        <v>587164.87582352769</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -3629,11 +3600,11 @@
         <v>3.34</v>
       </c>
       <c r="G9" s="24">
-        <v>249487.71279999998</v>
+        <v>170340</v>
       </c>
       <c r="H9" s="29">
         <f>G9</f>
-        <v>249487.71279999998</v>
+        <v>170340</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>119</v>
@@ -3669,18 +3640,18 @@
         <v>51</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E10" s="34"/>
       <c r="F10" s="1">
         <v>3.33</v>
       </c>
       <c r="G10" s="24">
-        <v>248740.74360000002</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="H10" s="29">
         <f>G10</f>
-        <v>248740.74360000002</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>119</v>
@@ -3723,11 +3694,11 @@
         <v>3.32</v>
       </c>
       <c r="G11" s="24">
-        <v>247993.77439999999</v>
+        <v>169320</v>
       </c>
       <c r="H11" s="29">
         <f>G11</f>
-        <v>247993.77439999999</v>
+        <v>169320</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>119</v>
@@ -3770,11 +3741,11 @@
         <v>3.33</v>
       </c>
       <c r="G12" s="24">
-        <v>248740.74360000002</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="H12" s="29">
         <f>G12</f>
-        <v>248740.74360000002</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>119</v>
@@ -3813,17 +3784,16 @@
         <v>88</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F13" s="1">
         <v>3.24</v>
       </c>
       <c r="G13" s="24">
-        <v>339465.83373000496</v>
+        <v>262705.83373000496</v>
       </c>
       <c r="H13" s="29">
-        <f>242000</f>
-        <v>242000</v>
+        <v>165240</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>119</v>
@@ -3850,7 +3820,7 @@
         <v>278468.18375380524</v>
       </c>
       <c r="R13" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -3865,24 +3835,24 @@
         <v>89</v>
       </c>
       <c r="E14" s="144" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F14" s="145">
         <v>3.33</v>
       </c>
       <c r="G14" s="146">
-        <v>825804.7268532</v>
+        <v>169300</v>
       </c>
       <c r="H14" s="147">
-        <f>61700+248741</f>
-        <v>310441</v>
+        <f>169300</f>
+        <v>169300</v>
       </c>
       <c r="I14" s="147" t="s">
         <v>119</v>
       </c>
       <c r="J14" s="148">
         <f t="shared" si="0"/>
-        <v>-515363.7268532</v>
+        <v>0</v>
       </c>
       <c r="K14" s="149">
         <f t="shared" si="1"/>
@@ -3897,11 +3867,11 @@
       </c>
       <c r="N14" s="152">
         <f>L14+K14-J14+M14</f>
-        <v>685193.7268532</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="O14" s="152">
         <f t="shared" si="3"/>
-        <v>726305.35046439199</v>
+        <v>180019.80000000002</v>
       </c>
       <c r="P14" s="11"/>
     </row>
@@ -3921,11 +3891,11 @@
         <v>3.32</v>
       </c>
       <c r="G15" s="24">
-        <v>247993.77885271999</v>
+        <v>169320</v>
       </c>
       <c r="H15" s="29">
         <f>G15</f>
-        <v>247993.77885271999</v>
+        <v>169320</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>119</v>
@@ -3968,17 +3938,17 @@
         <v>3.33</v>
       </c>
       <c r="G16" s="24">
-        <v>473876.30077040003</v>
+        <v>169706.30077040006</v>
       </c>
       <c r="H16" s="29">
-        <v>474000</v>
+        <v>170000</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>119</v>
       </c>
       <c r="J16" s="7">
         <f t="shared" si="0"/>
-        <v>123.6992295999662</v>
+        <v>293.6992295999371</v>
       </c>
       <c r="K16" s="38">
         <f t="shared" si="1"/>
@@ -3991,11 +3961,11 @@
       <c r="M16" s="23"/>
       <c r="N16" s="23">
         <f t="shared" si="4"/>
-        <v>169706.30077040006</v>
+        <v>169536.30077040009</v>
       </c>
       <c r="O16" s="23">
         <f t="shared" si="3"/>
-        <v>179888.67881662407</v>
+        <v>179708.47881662409</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -4014,18 +3984,18 @@
         <v>3.24</v>
       </c>
       <c r="G17" s="24">
-        <v>241532.39755877244</v>
+        <v>165275.34635877245</v>
       </c>
       <c r="H17" s="29">
-        <f>364000-H30</f>
-        <v>241497.05120000002</v>
+        <f>249000-H30</f>
+        <v>165360</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>119</v>
       </c>
       <c r="J17" s="7">
         <f t="shared" si="0"/>
-        <v>-35.346358772425447</v>
+        <v>84.65364122754545</v>
       </c>
       <c r="K17" s="38">
         <f t="shared" si="1"/>
@@ -4038,11 +4008,11 @@
       <c r="M17" s="23"/>
       <c r="N17" s="23">
         <f t="shared" si="4"/>
-        <v>165275.34635877245</v>
+        <v>165155.34635877248</v>
       </c>
       <c r="O17" s="23">
         <f t="shared" si="3"/>
-        <v>175191.8671402988</v>
+        <v>175064.66714029884</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -4057,23 +4027,23 @@
         <v>93</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F18" s="1">
         <v>3.33</v>
       </c>
       <c r="G18" s="24">
-        <v>248481.48720000003</v>
+        <v>179744.71643200007</v>
       </c>
       <c r="H18" s="29">
-        <v>248741</v>
+        <v>175000</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>119</v>
       </c>
       <c r="J18" s="7">
         <f t="shared" si="0"/>
-        <v>259.51279999996768</v>
+        <v>-4744.7164320000738</v>
       </c>
       <c r="K18" s="38">
         <f t="shared" si="1"/>
@@ -4086,11 +4056,11 @@
       <c r="M18" s="23"/>
       <c r="N18" s="23">
         <f t="shared" si="4"/>
-        <v>169570.48720000006</v>
+        <v>174574.7164320001</v>
       </c>
       <c r="O18" s="23">
         <f t="shared" si="3"/>
-        <v>179744.71643200007</v>
+        <v>185049.19941792011</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -4109,15 +4079,15 @@
         <v>3.32</v>
       </c>
       <c r="G19" s="24">
-        <v>972559.48738125595</v>
+        <v>1141879.487381256</v>
       </c>
       <c r="H19" s="29"/>
       <c r="I19" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J19" s="7">
         <f>H19-G19</f>
-        <v>-972559.48738125595</v>
+        <v>-1141879.487381256</v>
       </c>
       <c r="K19" s="38">
         <f t="shared" si="1"/>
@@ -4127,14 +4097,17 @@
         <f t="shared" si="2"/>
         <v>169320</v>
       </c>
-      <c r="M19" s="23"/>
+      <c r="M19" s="154">
+        <f>74376+19000</f>
+        <v>93376</v>
+      </c>
       <c r="N19" s="23">
         <f t="shared" si="4"/>
-        <v>1141879.487381256</v>
+        <v>1404575.487381256</v>
       </c>
       <c r="O19" s="23">
         <f t="shared" si="3"/>
-        <v>1210392.2566241312</v>
+        <v>1488850.0166241312</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -4153,15 +4126,15 @@
         <v>3.33</v>
       </c>
       <c r="G20" s="13">
-        <v>2605630.7121669492</v>
+        <v>2775460.7121669492</v>
       </c>
       <c r="H20" s="29"/>
       <c r="I20" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J20" s="41">
         <f t="shared" si="0"/>
-        <v>-2605630.7121669492</v>
+        <v>-2775460.7121669492</v>
       </c>
       <c r="K20" s="38">
         <f t="shared" si="1"/>
@@ -4171,16 +4144,14 @@
         <f t="shared" si="2"/>
         <v>169830.00000000003</v>
       </c>
-      <c r="M20" s="6">
-        <v>0</v>
-      </c>
+      <c r="M20" s="6"/>
       <c r="N20" s="23">
         <f t="shared" si="4"/>
-        <v>2775460.7121669492</v>
+        <v>2945290.7121669492</v>
       </c>
       <c r="O20" s="23">
         <f t="shared" si="3"/>
-        <v>2941988.3548969659</v>
+        <v>3122008.1548969662</v>
       </c>
       <c r="R20" s="30"/>
     </row>
@@ -4196,20 +4167,20 @@
         <v>96</v>
       </c>
       <c r="E21" s="34" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F21" s="1">
         <v>3.24</v>
       </c>
       <c r="G21" s="24">
-        <v>242018.02080000003</v>
+        <v>165240.00000000003</v>
       </c>
       <c r="H21" s="29">
         <f>G21</f>
-        <v>242018.02080000003</v>
+        <v>165240.00000000003</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J21" s="7">
         <f t="shared" si="0"/>
@@ -4223,7 +4194,7 @@
         <f t="shared" si="2"/>
         <v>165240.00000000003</v>
       </c>
-      <c r="M21" s="23"/>
+      <c r="M21" s="154"/>
       <c r="N21" s="23">
         <f t="shared" si="4"/>
         <v>165240.00000000003</v>
@@ -4249,17 +4220,18 @@
         <v>3.24</v>
       </c>
       <c r="G22" s="24">
-        <v>241557.12080000003</v>
+        <v>164797.12080000006</v>
       </c>
       <c r="H22" s="29">
-        <v>242000</v>
+        <f>G22</f>
+        <v>164797.12080000006</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J22" s="7">
         <f t="shared" si="0"/>
-        <v>442.87919999996666</v>
+        <v>0</v>
       </c>
       <c r="K22" s="38">
         <f t="shared" si="1"/>
@@ -4272,11 +4244,11 @@
       <c r="M22" s="23"/>
       <c r="N22" s="23">
         <f t="shared" si="4"/>
-        <v>164797.12080000006</v>
+        <v>165240.00000000003</v>
       </c>
       <c r="O22" s="23">
         <f t="shared" si="3"/>
-        <v>174684.94804800008</v>
+        <v>175154.40000000002</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -4291,24 +4263,24 @@
         <v>98</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F23" s="1">
         <v>3.32</v>
       </c>
       <c r="G23" s="24">
-        <v>247989.52914799986</v>
+        <v>169312.47794799984</v>
       </c>
       <c r="H23" s="29">
-        <f>370500-H31</f>
-        <v>247997.05120000002</v>
+        <f>252952-H31</f>
+        <v>169312</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J23" s="7">
         <f t="shared" si="0"/>
-        <v>7.522052000160329</v>
+        <v>-0.47794799983967096</v>
       </c>
       <c r="K23" s="38">
         <f t="shared" si="1"/>
@@ -4321,11 +4293,11 @@
       <c r="M23" s="23"/>
       <c r="N23" s="23">
         <f t="shared" si="4"/>
-        <v>169312.47794799984</v>
+        <v>169320.47794799984</v>
       </c>
       <c r="O23" s="23">
         <f t="shared" si="3"/>
-        <v>179471.22662487984</v>
+        <v>179479.70662487982</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -4340,20 +4312,20 @@
         <v>99</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F24" s="1">
         <v>3.33</v>
       </c>
       <c r="G24" s="17">
-        <v>248741.48720000003</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="H24" s="29">
         <f>G24</f>
-        <v>248741.48720000003</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J24" s="7">
         <f t="shared" si="0"/>
@@ -4389,20 +4361,20 @@
         <v>100</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F25" s="1">
         <v>3.24</v>
       </c>
       <c r="G25" s="24">
-        <v>242018.02080000003</v>
+        <v>165240.00000000003</v>
       </c>
       <c r="H25" s="29">
         <f>G25</f>
-        <v>242018.02080000003</v>
+        <v>165240.00000000003</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J25" s="7">
         <f t="shared" si="0"/>
@@ -4442,18 +4414,18 @@
         <v>3.33</v>
       </c>
       <c r="G26" s="24">
-        <v>248741.54860100005</v>
+        <v>169830.44620100007</v>
       </c>
       <c r="H26" s="29">
-        <f>493747-H35-H34</f>
-        <v>248741.1024</v>
+        <f>G26</f>
+        <v>169830.44620100007</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="J26" s="7">
         <f t="shared" si="0"/>
-        <v>-0.44620100004249252</v>
+        <v>0</v>
       </c>
       <c r="K26" s="38">
         <f t="shared" si="1"/>
@@ -4466,11 +4438,11 @@
       <c r="M26" s="23"/>
       <c r="N26" s="23">
         <f t="shared" si="4"/>
-        <v>169830.44620100007</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="O26" s="23">
         <f t="shared" si="3"/>
-        <v>180020.27297306008</v>
+        <v>180019.80000000002</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -4485,23 +4457,23 @@
         <v>102</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F27" s="1">
         <v>3.32</v>
       </c>
       <c r="G27" s="17">
-        <v>247993.77491239994</v>
+        <v>169313.77491239994</v>
       </c>
       <c r="H27" s="29">
-        <v>248000</v>
+        <v>170000</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J27" s="7">
         <f t="shared" si="0"/>
-        <v>6.2250876000616699</v>
+        <v>686.22508760006167</v>
       </c>
       <c r="K27" s="38">
         <f t="shared" si="1"/>
@@ -4514,14 +4486,14 @@
       <c r="M27" s="23"/>
       <c r="N27" s="23">
         <f t="shared" si="4"/>
-        <v>169313.77491239994</v>
+        <v>168633.77491239994</v>
       </c>
       <c r="O27" s="23">
         <f t="shared" si="3"/>
-        <v>179472.60140714393</v>
+        <v>178751.80140714394</v>
       </c>
       <c r="Q27" s="143" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -4536,20 +4508,20 @@
         <v>103</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F28" s="1">
         <v>3.33</v>
       </c>
       <c r="G28" s="24">
-        <v>248740.74360000002</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="H28" s="29">
         <f>G28</f>
-        <v>248740.74360000002</v>
+        <v>169830.00000000003</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J28" s="7">
         <f t="shared" si="0"/>
@@ -4583,22 +4555,22 @@
         <v>70</v>
       </c>
       <c r="D29" s="140" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F29" s="1">
         <v>3.24</v>
       </c>
       <c r="G29" s="24">
-        <v>876297.05374809331</v>
+        <v>899519.05374809331</v>
       </c>
       <c r="H29" s="29">
-        <v>142018</v>
+        <v>165240</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J29" s="7">
         <f t="shared" si="0"/>
@@ -4612,14 +4584,17 @@
         <f t="shared" si="2"/>
         <v>165240.00000000003</v>
       </c>
-      <c r="M29" s="23"/>
+      <c r="M29" s="154">
+        <f>74376+19000</f>
+        <v>93376</v>
+      </c>
       <c r="N29" s="23">
         <f>L29+K29-J29+M29</f>
-        <v>899519.05374809331</v>
+        <v>992895.05374809331</v>
       </c>
       <c r="O29" s="23">
         <f t="shared" si="3"/>
-        <v>953490.19697297888</v>
+        <v>1052468.7569729788</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -4638,14 +4613,14 @@
         <v>1.64</v>
       </c>
       <c r="G30" s="24">
-        <v>122502.94879999998</v>
+        <v>83639.999999999985</v>
       </c>
       <c r="H30" s="29">
         <f>G30</f>
-        <v>122502.94879999998</v>
+        <v>83639.999999999985</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J30" s="7">
         <f t="shared" si="0"/>
@@ -4685,14 +4660,14 @@
         <v>1.64</v>
       </c>
       <c r="G31" s="24">
-        <v>122502.94879999998</v>
+        <v>83639.999999999985</v>
       </c>
       <c r="H31" s="29">
         <f>G31</f>
-        <v>122502.94879999998</v>
+        <v>83639.999999999985</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J31" s="7">
         <f t="shared" si="0"/>
@@ -4732,17 +4707,17 @@
         <v>1.64</v>
       </c>
       <c r="G32" s="24">
-        <v>189669.73443736721</v>
+        <v>208309.73443736718</v>
       </c>
       <c r="H32" s="29">
         <v>65000</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J32" s="7">
         <f t="shared" si="0"/>
-        <v>-124669.73443736721</v>
+        <v>-143309.73443736718</v>
       </c>
       <c r="K32" s="38">
         <f t="shared" si="1"/>
@@ -4755,11 +4730,11 @@
       <c r="M32" s="23"/>
       <c r="N32" s="23">
         <f t="shared" si="4"/>
-        <v>208309.73443736718</v>
+        <v>226949.73443736718</v>
       </c>
       <c r="O32" s="23">
         <f t="shared" si="3"/>
-        <v>220808.31850360922</v>
+        <v>240566.71850360921</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
@@ -4778,15 +4753,15 @@
         <v>1.64</v>
       </c>
       <c r="G33" s="24">
-        <v>385386.30447480001</v>
+        <v>469026.30447480001</v>
       </c>
       <c r="H33" s="29"/>
       <c r="I33" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J33" s="7">
         <f t="shared" si="0"/>
-        <v>-385386.30447480001</v>
+        <v>-469026.30447480001</v>
       </c>
       <c r="K33" s="38">
         <f t="shared" si="1"/>
@@ -4799,14 +4774,14 @@
       <c r="M33" s="23"/>
       <c r="N33" s="23">
         <f t="shared" si="4"/>
-        <v>469026.30447480001</v>
+        <v>552666.30447480001</v>
       </c>
       <c r="O33" s="23">
         <f t="shared" si="3"/>
-        <v>497167.88274328801</v>
+        <v>585826.28274328797</v>
       </c>
       <c r="Q33" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
@@ -4825,18 +4800,15 @@
         <v>1.64</v>
       </c>
       <c r="G34" s="24">
-        <v>122502.94879999998</v>
-      </c>
-      <c r="H34" s="29">
-        <f>G34</f>
-        <v>122502.94879999998</v>
-      </c>
+        <v>83639.999999999985</v>
+      </c>
+      <c r="H34" s="29"/>
       <c r="I34" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J34" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-83639.999999999985</v>
       </c>
       <c r="K34" s="38">
         <f t="shared" si="1"/>
@@ -4849,11 +4821,11 @@
       <c r="M34" s="23"/>
       <c r="N34" s="23">
         <f t="shared" si="4"/>
-        <v>83639.999999999985</v>
+        <v>167279.99999999997</v>
       </c>
       <c r="O34" s="23">
         <f t="shared" si="3"/>
-        <v>88658.39999999998</v>
+        <v>177316.79999999996</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
@@ -4872,11 +4844,11 @@
         <v>1.64</v>
       </c>
       <c r="G35" s="24">
-        <v>122502.94879999998</v>
+        <v>83639.999999999985</v>
       </c>
       <c r="H35" s="29">
         <f>G35</f>
-        <v>122502.94879999998</v>
+        <v>83639.999999999985</v>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="7">
@@ -4917,15 +4889,15 @@
         <v>1.64</v>
       </c>
       <c r="G36" s="142">
-        <v>1238434.7826287674</v>
+        <v>1322074.7826287674</v>
       </c>
       <c r="H36" s="29"/>
       <c r="I36" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J36" s="7">
         <f t="shared" si="0"/>
-        <v>-1238434.7826287674</v>
+        <v>-1322074.7826287674</v>
       </c>
       <c r="K36" s="38">
         <f t="shared" si="1"/>
@@ -4938,11 +4910,11 @@
       <c r="M36" s="23"/>
       <c r="N36" s="23">
         <f t="shared" si="4"/>
-        <v>1322074.7826287674</v>
+        <v>1405714.7826287674</v>
       </c>
       <c r="O36" s="23">
         <f t="shared" si="3"/>
-        <v>1401399.2695864935</v>
+        <v>1490057.6695864934</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
@@ -4961,14 +4933,14 @@
         <v>1.64</v>
       </c>
       <c r="G37" s="24">
-        <v>122502.94879999998</v>
+        <v>83639.999999999985</v>
       </c>
       <c r="H37" s="29">
         <f>G37</f>
-        <v>122502.94879999998</v>
+        <v>83639.999999999985</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J37" s="7">
         <f t="shared" si="0"/>
@@ -5003,25 +4975,20 @@
       <c r="D38" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="E38" s="34" t="s">
-        <v>145</v>
-      </c>
+      <c r="E38" s="34"/>
       <c r="F38" s="1">
         <v>1.64</v>
       </c>
       <c r="G38" s="24">
-        <v>122502.94879999998</v>
-      </c>
-      <c r="H38" s="29">
-        <f>G38</f>
-        <v>122502.94879999998</v>
-      </c>
+        <v>83639.999999999985</v>
+      </c>
+      <c r="H38" s="29"/>
       <c r="I38" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J38" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-83639.999999999985</v>
       </c>
       <c r="K38" s="38">
         <f t="shared" si="1"/>
@@ -5034,11 +5001,11 @@
       <c r="M38" s="23"/>
       <c r="N38" s="23">
         <f t="shared" si="4"/>
-        <v>83639.999999999985</v>
+        <v>167279.99999999997</v>
       </c>
       <c r="O38" s="23">
         <f t="shared" si="3"/>
-        <v>88658.39999999998</v>
+        <v>177316.79999999996</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
@@ -5057,18 +5024,18 @@
         <v>1.64</v>
       </c>
       <c r="G39" s="24">
-        <v>115411.22160559986</v>
+        <v>83640.001605599842</v>
       </c>
       <c r="H39" s="29">
-        <f>80000+35411.22</f>
-        <v>115411.22</v>
+        <f>G39</f>
+        <v>83640.001605599842</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J39" s="7">
         <f>H39-G39</f>
-        <v>-1.6055998567026109E-3</v>
+        <v>0</v>
       </c>
       <c r="K39" s="38">
         <f t="shared" si="1"/>
@@ -5081,11 +5048,11 @@
       <c r="M39" s="23"/>
       <c r="N39" s="23">
         <f t="shared" si="4"/>
-        <v>83640.001605599842</v>
+        <v>83639.999999999985</v>
       </c>
       <c r="O39" s="23">
         <f t="shared" si="3"/>
-        <v>88658.401701935829</v>
+        <v>88658.39999999998</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
@@ -5104,7 +5071,7 @@
         <v>1.64</v>
       </c>
       <c r="G40" s="24">
-        <v>268868.98363898392</v>
+        <v>352508.98363898392</v>
       </c>
       <c r="H40" s="29"/>
       <c r="I40" s="13" t="s">
@@ -5112,7 +5079,7 @@
       </c>
       <c r="J40" s="7">
         <f t="shared" si="0"/>
-        <v>-268868.98363898392</v>
+        <v>-352508.98363898392</v>
       </c>
       <c r="K40" s="38">
         <f t="shared" si="1"/>
@@ -5125,11 +5092,11 @@
       <c r="M40" s="23"/>
       <c r="N40" s="23">
         <f t="shared" si="4"/>
-        <v>352508.98363898392</v>
+        <v>436148.98363898392</v>
       </c>
       <c r="O40" s="23">
         <f t="shared" si="3"/>
-        <v>373659.52265732293</v>
+        <v>462317.92265732295</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -5144,16 +5111,16 @@
       </c>
       <c r="G41" s="9">
         <f>SUM(G5:G40)</f>
-        <v>14248543.900368586</v>
+        <v>12113881.208294673</v>
       </c>
       <c r="H41" s="9">
         <f>SUM(H5:H40)</f>
-        <v>6733533.1944527216</v>
+        <v>4309319.5686066002</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="135">
         <f t="shared" ref="J41:O41" si="5">SUM(J5:J40)</f>
-        <v>-7515010.7059158729</v>
+        <v>-7804561.6396880727</v>
       </c>
       <c r="K41" s="9">
         <f t="shared" si="5"/>
@@ -5165,15 +5132,15 @@
       </c>
       <c r="M41" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>186752</v>
       </c>
       <c r="N41" s="10">
         <f t="shared" si="5"/>
-        <v>12619600.705915872</v>
+        <v>13095903.639688073</v>
       </c>
       <c r="O41" s="9">
         <f t="shared" si="5"/>
-        <v>13376776.748270832</v>
+        <v>13881657.858069362</v>
       </c>
     </row>
     <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5182,7 +5149,7 @@
       </c>
       <c r="I42">
         <f>SUMIF(I5:I40,"b",H5:H40)</f>
-        <v>6362289.1432527211</v>
+        <v>4055849.1224055998</v>
       </c>
       <c r="L42" s="11"/>
     </row>
@@ -5192,7 +5159,7 @@
       </c>
       <c r="I43">
         <f>SUMIF(I5:I40,"e",H5:H40)</f>
-        <v>248741.1024</v>
+        <v>169830.44620100007</v>
       </c>
     </row>
     <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
@@ -5201,77 +5168,77 @@
       </c>
       <c r="H44" s="35">
         <f>I42+I43</f>
-        <v>6611030.2456527213</v>
+        <v>4225679.5686066002</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D47" s="182" t="s">
-        <v>180</v>
-      </c>
-      <c r="E47" s="182"/>
-      <c r="F47" s="182"/>
-      <c r="G47" s="182"/>
-      <c r="H47" s="182"/>
-      <c r="I47" s="182"/>
-      <c r="J47" s="182"/>
-      <c r="K47" s="182"/>
-      <c r="L47" s="182"/>
-      <c r="M47" s="182"/>
-      <c r="N47" s="182"/>
+      <c r="D47" s="177" t="s">
+        <v>176</v>
+      </c>
+      <c r="E47" s="177"/>
+      <c r="F47" s="177"/>
+      <c r="G47" s="177"/>
+      <c r="H47" s="177"/>
+      <c r="I47" s="177"/>
+      <c r="J47" s="177"/>
+      <c r="K47" s="177"/>
+      <c r="L47" s="177"/>
+      <c r="M47" s="177"/>
+      <c r="N47" s="177"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="D48" s="182"/>
-      <c r="E48" s="182"/>
-      <c r="F48" s="182"/>
-      <c r="G48" s="182"/>
-      <c r="H48" s="182"/>
-      <c r="I48" s="182"/>
-      <c r="J48" s="182"/>
-      <c r="K48" s="182"/>
-      <c r="L48" s="182"/>
-      <c r="M48" s="182"/>
-      <c r="N48" s="182"/>
+      <c r="D48" s="177"/>
+      <c r="E48" s="177"/>
+      <c r="F48" s="177"/>
+      <c r="G48" s="177"/>
+      <c r="H48" s="177"/>
+      <c r="I48" s="177"/>
+      <c r="J48" s="177"/>
+      <c r="K48" s="177"/>
+      <c r="L48" s="177"/>
+      <c r="M48" s="177"/>
+      <c r="N48" s="177"/>
     </row>
     <row r="49" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D49" s="182"/>
-      <c r="E49" s="182"/>
-      <c r="F49" s="182"/>
-      <c r="G49" s="182"/>
-      <c r="H49" s="182"/>
-      <c r="I49" s="182"/>
-      <c r="J49" s="182"/>
-      <c r="K49" s="182"/>
-      <c r="L49" s="182"/>
-      <c r="M49" s="182"/>
-      <c r="N49" s="182"/>
+      <c r="D49" s="177"/>
+      <c r="E49" s="177"/>
+      <c r="F49" s="177"/>
+      <c r="G49" s="177"/>
+      <c r="H49" s="177"/>
+      <c r="I49" s="177"/>
+      <c r="J49" s="177"/>
+      <c r="K49" s="177"/>
+      <c r="L49" s="177"/>
+      <c r="M49" s="177"/>
+      <c r="N49" s="177"/>
     </row>
     <row r="50" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D50" s="182"/>
-      <c r="E50" s="182"/>
-      <c r="F50" s="182"/>
-      <c r="G50" s="182"/>
-      <c r="H50" s="182"/>
-      <c r="I50" s="182"/>
-      <c r="J50" s="182"/>
-      <c r="K50" s="182"/>
-      <c r="L50" s="182"/>
-      <c r="M50" s="182"/>
-      <c r="N50" s="182"/>
+      <c r="D50" s="177"/>
+      <c r="E50" s="177"/>
+      <c r="F50" s="177"/>
+      <c r="G50" s="177"/>
+      <c r="H50" s="177"/>
+      <c r="I50" s="177"/>
+      <c r="J50" s="177"/>
+      <c r="K50" s="177"/>
+      <c r="L50" s="177"/>
+      <c r="M50" s="177"/>
+      <c r="N50" s="177"/>
     </row>
     <row r="51" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D51" s="182"/>
-      <c r="E51" s="182"/>
-      <c r="F51" s="182"/>
-      <c r="G51" s="182"/>
-      <c r="H51" s="182"/>
-      <c r="I51" s="182"/>
-      <c r="J51" s="182"/>
-      <c r="K51" s="182"/>
-      <c r="L51" s="182"/>
-      <c r="M51" s="182"/>
-      <c r="N51" s="182"/>
+      <c r="D51" s="177"/>
+      <c r="E51" s="177"/>
+      <c r="F51" s="177"/>
+      <c r="G51" s="177"/>
+      <c r="H51" s="177"/>
+      <c r="I51" s="177"/>
+      <c r="J51" s="177"/>
+      <c r="K51" s="177"/>
+      <c r="L51" s="177"/>
+      <c r="M51" s="177"/>
+      <c r="N51" s="177"/>
     </row>
     <row r="52" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D52" s="153"/>
@@ -5318,28 +5285,28 @@
   <sheetData>
     <row r="6" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E7" s="190" t="s">
-        <v>154</v>
-      </c>
-      <c r="F7" s="191"/>
-      <c r="G7" s="191"/>
-      <c r="H7" s="191"/>
-      <c r="I7" s="191"/>
-      <c r="J7" s="191"/>
-      <c r="K7" s="189"/>
+      <c r="E7" s="192" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="193"/>
+      <c r="G7" s="193"/>
+      <c r="H7" s="193"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="193"/>
+      <c r="K7" s="191"/>
       <c r="L7" s="42"/>
       <c r="M7" s="43"/>
     </row>
     <row r="8" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E8" s="192" t="s">
-        <v>155</v>
-      </c>
-      <c r="F8" s="191"/>
-      <c r="G8" s="191"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="191"/>
-      <c r="J8" s="191"/>
-      <c r="K8" s="189"/>
+      <c r="E8" s="194" t="s">
+        <v>151</v>
+      </c>
+      <c r="F8" s="193"/>
+      <c r="G8" s="193"/>
+      <c r="H8" s="193"/>
+      <c r="I8" s="193"/>
+      <c r="J8" s="193"/>
+      <c r="K8" s="191"/>
       <c r="L8" s="44"/>
       <c r="M8" s="45"/>
     </row>
@@ -5350,7 +5317,7 @@
       <c r="H9" s="46"/>
       <c r="I9" s="47"/>
       <c r="J9" s="47" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="K9" s="45"/>
       <c r="L9" s="44"/>
@@ -5358,14 +5325,14 @@
     </row>
     <row r="10" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E10" s="44" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F10" s="47"/>
       <c r="G10" s="47"/>
       <c r="H10" s="47"/>
       <c r="I10" s="47"/>
       <c r="J10" s="47" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K10" s="45"/>
       <c r="L10" s="44"/>
@@ -5383,15 +5350,15 @@
       <c r="M11" s="45"/>
     </row>
     <row r="12" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E12" s="193" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12" s="194"/>
-      <c r="G12" s="194"/>
-      <c r="H12" s="194"/>
-      <c r="I12" s="194"/>
-      <c r="J12" s="194"/>
-      <c r="K12" s="195"/>
+      <c r="E12" s="195" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="196"/>
+      <c r="G12" s="196"/>
+      <c r="H12" s="196"/>
+      <c r="I12" s="196"/>
+      <c r="J12" s="196"/>
+      <c r="K12" s="197"/>
       <c r="L12" s="44"/>
       <c r="M12" s="45"/>
     </row>
@@ -5408,7 +5375,7 @@
     </row>
     <row r="14" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E14" s="44" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F14" s="47"/>
       <c r="G14" s="47" t="str">
@@ -5417,20 +5384,20 @@
       </c>
       <c r="H14" s="47"/>
       <c r="I14" s="47" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J14" s="51">
         <v>45600</v>
       </c>
       <c r="K14" s="45"/>
-      <c r="L14" s="183" t="s">
-        <v>162</v>
-      </c>
-      <c r="M14" s="184"/>
+      <c r="L14" s="185" t="s">
+        <v>158</v>
+      </c>
+      <c r="M14" s="186"/>
     </row>
     <row r="15" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E15" s="44" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F15" s="52" t="str">
         <f>PRORRATEO!C10</f>
@@ -5452,8 +5419,8 @@
       <c r="I16" s="47"/>
       <c r="J16" s="47"/>
       <c r="K16" s="45"/>
-      <c r="L16" s="185"/>
-      <c r="M16" s="184"/>
+      <c r="L16" s="187"/>
+      <c r="M16" s="186"/>
     </row>
     <row r="17" spans="5:15" x14ac:dyDescent="0.3">
       <c r="E17" s="44"/>
@@ -5489,45 +5456,45 @@
       <c r="M19" s="54"/>
     </row>
     <row r="20" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E20" s="186" t="s">
-        <v>164</v>
-      </c>
-      <c r="F20" s="187"/>
-      <c r="G20" s="187"/>
-      <c r="H20" s="187"/>
-      <c r="I20" s="187"/>
-      <c r="J20" s="188">
+      <c r="E20" s="188" t="s">
+        <v>160</v>
+      </c>
+      <c r="F20" s="189"/>
+      <c r="G20" s="189"/>
+      <c r="H20" s="189"/>
+      <c r="I20" s="189"/>
+      <c r="J20" s="190">
         <f>PRORRATEO!H10</f>
-        <v>248740.74360000002</v>
-      </c>
-      <c r="K20" s="189"/>
+        <v>169830.00000000003</v>
+      </c>
+      <c r="K20" s="191"/>
       <c r="L20" s="55"/>
       <c r="M20" s="56"/>
     </row>
     <row r="24" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="25" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G25" s="190" t="s">
-        <v>154</v>
-      </c>
-      <c r="H25" s="191"/>
-      <c r="I25" s="191"/>
-      <c r="J25" s="191"/>
-      <c r="K25" s="191"/>
-      <c r="L25" s="191"/>
-      <c r="M25" s="189"/>
+      <c r="G25" s="192" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" s="193"/>
+      <c r="I25" s="193"/>
+      <c r="J25" s="193"/>
+      <c r="K25" s="193"/>
+      <c r="L25" s="193"/>
+      <c r="M25" s="191"/>
       <c r="N25" s="42"/>
       <c r="O25" s="43"/>
     </row>
     <row r="26" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G26" s="192" t="s">
-        <v>155</v>
-      </c>
-      <c r="H26" s="191"/>
-      <c r="I26" s="191"/>
-      <c r="J26" s="191"/>
-      <c r="K26" s="191"/>
-      <c r="L26" s="191"/>
-      <c r="M26" s="189"/>
+      <c r="G26" s="194" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26" s="193"/>
+      <c r="I26" s="193"/>
+      <c r="J26" s="193"/>
+      <c r="K26" s="193"/>
+      <c r="L26" s="193"/>
+      <c r="M26" s="191"/>
       <c r="N26" s="44"/>
       <c r="O26" s="45"/>
     </row>
@@ -5538,7 +5505,7 @@
       <c r="J27" s="46"/>
       <c r="K27" s="47"/>
       <c r="L27" s="47" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M27" s="45"/>
       <c r="N27" s="44"/>
@@ -5546,14 +5513,14 @@
     </row>
     <row r="28" spans="5:15" x14ac:dyDescent="0.3">
       <c r="G28" s="44" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H28" s="47"/>
       <c r="I28" s="47"/>
       <c r="J28" s="47"/>
       <c r="K28" s="47"/>
       <c r="L28" s="47" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="M28" s="45"/>
       <c r="N28" s="44"/>
@@ -5571,15 +5538,15 @@
       <c r="O29" s="45"/>
     </row>
     <row r="30" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="G30" s="193" t="s">
-        <v>159</v>
-      </c>
-      <c r="H30" s="194"/>
-      <c r="I30" s="194"/>
-      <c r="J30" s="194"/>
-      <c r="K30" s="194"/>
-      <c r="L30" s="194"/>
-      <c r="M30" s="195"/>
+      <c r="G30" s="195" t="s">
+        <v>155</v>
+      </c>
+      <c r="H30" s="196"/>
+      <c r="I30" s="196"/>
+      <c r="J30" s="196"/>
+      <c r="K30" s="196"/>
+      <c r="L30" s="196"/>
+      <c r="M30" s="197"/>
       <c r="N30" s="44"/>
       <c r="O30" s="45"/>
     </row>
@@ -5596,26 +5563,26 @@
     </row>
     <row r="32" spans="5:15" x14ac:dyDescent="0.3">
       <c r="G32" s="44" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H32" s="47"/>
       <c r="I32" s="47"/>
       <c r="J32" s="47"/>
       <c r="K32" s="47" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="L32" s="51">
         <v>45600</v>
       </c>
       <c r="M32" s="45"/>
-      <c r="N32" s="183" t="s">
-        <v>162</v>
-      </c>
-      <c r="O32" s="184"/>
+      <c r="N32" s="185" t="s">
+        <v>158</v>
+      </c>
+      <c r="O32" s="186"/>
     </row>
     <row r="33" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G33" s="44" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H33" s="52" t="str">
         <f>PRORRATEO!E28</f>
@@ -5637,8 +5604,8 @@
       <c r="K34" s="47"/>
       <c r="L34" s="47"/>
       <c r="M34" s="45"/>
-      <c r="N34" s="185"/>
-      <c r="O34" s="184"/>
+      <c r="N34" s="187"/>
+      <c r="O34" s="186"/>
     </row>
     <row r="35" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G35" s="44"/>
@@ -5674,18 +5641,18 @@
       <c r="O37" s="54"/>
     </row>
     <row r="38" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G38" s="186" t="s">
-        <v>164</v>
-      </c>
-      <c r="H38" s="187"/>
-      <c r="I38" s="187"/>
-      <c r="J38" s="187"/>
-      <c r="K38" s="187"/>
-      <c r="L38" s="188">
+      <c r="G38" s="188" t="s">
+        <v>160</v>
+      </c>
+      <c r="H38" s="189"/>
+      <c r="I38" s="189"/>
+      <c r="J38" s="189"/>
+      <c r="K38" s="189"/>
+      <c r="L38" s="190">
         <f>PRORRATEO!J28</f>
         <v>0</v>
       </c>
-      <c r="M38" s="189"/>
+      <c r="M38" s="191"/>
       <c r="N38" s="55"/>
       <c r="O38" s="56"/>
     </row>
